--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0238.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0238.xlsx
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Crossworld Sync: Pt. 1</t>
+          <t>Đồng Bộ Thế Giới: Phần 1</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Crossworld Sync: Pt. 2</t>
+          <t>Đồng Bộ Thế Giới: Phần 2</t>
         </is>
       </c>
     </row>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bị hạ gục bởi đòn tấn công của Denia.</t>
+          <t>Một Resonator bị hạ gục bởi đòn tấn công của Denia.</t>
         </is>
       </c>
     </row>
@@ -13393,7 +13393,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bị hạ gục bởi đòn tấn công của Voidwing Moth.</t>
+          <t>Một Resonator bị hạ gục bởi đòn tấn công của Voidwing Moth.</t>
         </is>
       </c>
     </row>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Dọn Dẹp Resources ({0})</t>
+          <t>Thanh Tẩy Tài Nguyên ({0})</t>
         </is>
       </c>
     </row>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>&lt;color=#f9ffffff&gt;{0}&lt;/color&gt;&lt;color=#f9ffff99&gt;/{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Rover hiện đang ở trong Vực Ảo Ảnh. Không thể chuyển đổi.</t>
+          <t>Vận Mệnh Giả hiện đang ở trong Vực Ảo Ảnh. Không thể chuyển đổi.</t>
         </is>
       </c>
     </row>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Vách đá sâu trong Lahai-Roi bị Voidmatter xâm thực. Nơi đây, ngay cả âm thanh cũng bị nuốt chửng.</t>
+          <t>Vách đá sâu trong lòng Lahai-Roi, nơi bị Voidmatter xâm thực. Âm thanh tại đây cũng bị nuốt chửng.</t>
         </is>
       </c>
     </row>
@@ -17748,7 +17748,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Xuất sắc! Bài Kiểm Tra Thành Thạo Combat!</t>
+          <t>Xuất sắc! Bài Kiểm Tra Thành Thạo Chiến Đấu!</t>
         </is>
       </c>
     </row>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Vào Chương trình Ký ức!</t>
+          <t>Tiến vào Chương Trình Ký Ức!</t>
         </is>
       </c>
     </row>
@@ -17943,7 +17943,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Xuất sắc! Bài Kiểm Tra Thành Thạo Combat!</t>
+          <t>Xuất sắc! Bài Kiểm Tra Thành Thạo Chiến Đấu!</t>
         </is>
       </c>
     </row>
@@ -18008,7 +18008,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Vào Chương trình Ký ức!</t>
+          <t>Tiến vào Chương Trình Ký Ức!</t>
         </is>
       </c>
     </row>
@@ -18074,8 +18074,8 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Bộ Khung Xe Pha Lê Bầu Trời
-Bao gồm Khung Xe Pha Lê Bầu Trời, Mẫu Xe "Tuyết, Trăng và Hoa" (Cản Trái, Cản Phải, Trước/Sau) và Astrites.</t>
+          <t>Bộ Khung Xe Astrite Bầu Trời
+Bao gồm Khung Xe Astrite Bầu Trời, Mẫu Xe "Tuyết, Trăng và Hoa" (Cản Trái, Cản Phải, Trước/Sau) và Astrites.</t>
         </is>
       </c>
     </row>
@@ -18207,7 +18207,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Sau bản cập nhật Phiên bản 3.3, tất cả ưu đãi nạp thẻ lần đầu 2x sẽ được thiết lập lại cho Lunite Mua.</t>
+          <t>Sau bản cập nhật Phiên bản 3.3, tất cả ưu đãi nạp thẻ lần đầu 2x sẽ được thiết lập lại cho Lunite Purchase.</t>
         </is>
       </c>
     </row>
@@ -18337,7 +18337,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Crossworld Sync: Pt. 1</t>
+          <t>Đồng Bộ Thế Giới: Phần 1</t>
         </is>
       </c>
     </row>
@@ -18402,7 +18402,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Crossworld Sync: Pt. 1</t>
+          <t>Đồng Bộ Thế Giới: Phần 1</t>
         </is>
       </c>
     </row>
@@ -18467,7 +18467,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Crossworld Sync: Pt. 1</t>
+          <t>Đồng Bộ Thế Giới: Phần 1</t>
         </is>
       </c>
     </row>
@@ -18532,7 +18532,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Crossworld Sync: Pt. 2</t>
+          <t>Đồng Bộ Thế Giới: Phần 2</t>
         </is>
       </c>
     </row>
@@ -18597,7 +18597,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Crossworld Sync: Pt. 2</t>
+          <t>Đồng Bộ Thế Giới: Phần 2</t>
         </is>
       </c>
     </row>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Crossworld Sync: Pt. 2</t>
+          <t>Đồng Bộ Thế Giới: Phần 2</t>
         </is>
       </c>
     </row>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Kaiju Không. 8</t>
+          <t>Kaiju Số 8</t>
         </is>
       </c>
     </row>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Sau bản cập nhật phiên bản, hệ thống phụ kiện mới sẽ được giới thiệu. Trang bị và thay đổi Phụ kiện cho Cộng Hưởng Giả trong trang Phụ kiện.</t>
+          <t>Sau bản cập nhật phiên bản, hệ thống phụ kiện mới sẽ được giới thiệu. Trang bị và thay đổi Phụ kiện cho Resonator trong trang Phụ kiện.</t>
         </is>
       </c>
     </row>
